--- a/kas.xlsx
+++ b/kas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kas musholla\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDA6F36-C63C-490D-8898-99368062FCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E64985-99BB-4503-BECC-110A1BC9311C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="7360" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -722,7 +722,9 @@
       <c r="C7" s="9">
         <v>2000</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="9">
+        <v>5000</v>
+      </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -923,7 +925,7 @@
       </c>
       <c r="D19" s="9">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>5200</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
@@ -961,7 +963,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:H19)</f>
-        <v>5377</v>
+        <v>10377</v>
       </c>
       <c r="J21" s="2">
         <v>17</v>
@@ -990,7 +992,7 @@
       <c r="C24" s="17"/>
       <c r="D24" s="10">
         <f>D21-K45</f>
-        <v>-48623</v>
+        <v>-43623</v>
       </c>
       <c r="J24" s="2">
         <v>20</v>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E64985-99BB-4503-BECC-110A1BC9311C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6321DAE0-7A0C-4B87-912D-39A074ABE0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="7360" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>data kas</t>
   </si>
@@ -114,16 +114,10 @@
     <t>total pengeluaran</t>
   </si>
   <si>
-    <t>beli ganja</t>
-  </si>
-  <si>
     <t>uang saat ini =</t>
   </si>
   <si>
-    <t>beli sabu</t>
-  </si>
-  <si>
-    <t>beli rokok</t>
+    <t>beli galon</t>
   </si>
 </sst>
 </file>
@@ -612,7 +606,8 @@
     <col min="2" max="2" width="10.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -677,54 +672,40 @@
         <v>1</v>
       </c>
       <c r="K5" s="8">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="9">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="9">
-        <v>200</v>
-      </c>
-      <c r="E6" s="9">
-        <v>200</v>
-      </c>
-      <c r="F6" s="9">
-        <v>577</v>
-      </c>
-      <c r="G6" s="9">
-        <v>200</v>
-      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
       <c r="H6" s="9">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="J6" s="2">
         <v>2</v>
       </c>
       <c r="K6" s="8">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="9">
-        <v>2000</v>
-      </c>
-      <c r="D7" s="9">
-        <v>5000</v>
-      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -732,12 +713,8 @@
       <c r="J7" s="2">
         <v>3</v>
       </c>
-      <c r="K7" s="8">
-        <v>50000</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
@@ -921,27 +898,27 @@
       </c>
       <c r="C19" s="9">
         <f t="shared" ref="C19:H19" si="0">SUM(C6:C18)</f>
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="D19" s="9">
         <f t="shared" si="0"/>
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F19" s="9">
         <f t="shared" si="0"/>
-        <v>577</v>
+        <v>0</v>
       </c>
       <c r="G19" s="9">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="J19" s="2">
         <v>15</v>
@@ -963,7 +940,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:H19)</f>
-        <v>10377</v>
+        <v>10000</v>
       </c>
       <c r="J21" s="2">
         <v>17</v>
@@ -987,12 +964,12 @@
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B24" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="10">
         <f>D21-K45</f>
-        <v>-43623</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2">
         <v>20</v>
@@ -1146,7 +1123,7 @@
       </c>
       <c r="K45" s="15">
         <f>SUM(K5:K44)</f>
-        <v>54000</v>
+        <v>10000</v>
       </c>
       <c r="L45" s="16"/>
     </row>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6321DAE0-7A0C-4B87-912D-39A074ABE0F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78C53E9-C3C2-4DCC-8CD0-F8ABAEDDA10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78C53E9-C3C2-4DCC-8CD0-F8ABAEDDA10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA799A3-9232-4BC0-BBE2-7D8C8EDECEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>data kas</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>beli galon</t>
+  </si>
+  <si>
+    <t>bg ade</t>
   </si>
 </sst>
 </file>
@@ -189,7 +192,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -207,15 +210,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -265,25 +259,23 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -607,7 +599,7 @@
     <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" customWidth="1"/>
     <col min="5" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -617,27 +609,28 @@
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="M3" s="14" t="s">
+      <c r="E3" s="17"/>
+      <c r="M3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="14"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
         <v>21</v>
       </c>
@@ -649,7 +642,7 @@
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="12"/>
+      <c r="B5" s="11"/>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -667,6 +660,9 @@
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="J5" s="2">
         <v>1</v>
@@ -690,6 +686,9 @@
       <c r="H6" s="9">
         <v>10000</v>
       </c>
+      <c r="I6" s="9">
+        <v>25000</v>
+      </c>
       <c r="J6" s="2">
         <v>2</v>
       </c>
@@ -710,6 +709,7 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
       <c r="J7" s="2">
         <v>3</v>
       </c>
@@ -726,6 +726,7 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
       <c r="J8" s="2">
         <v>4</v>
       </c>
@@ -742,6 +743,7 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="2">
         <v>5</v>
       </c>
@@ -758,6 +760,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
       <c r="J10" s="2">
         <v>6</v>
       </c>
@@ -774,6 +777,7 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="2">
         <v>7</v>
       </c>
@@ -790,6 +794,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="2">
         <v>8</v>
       </c>
@@ -806,6 +811,7 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
       <c r="J13" s="2">
         <v>9</v>
       </c>
@@ -822,6 +828,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
       <c r="J14" s="2">
         <v>10</v>
       </c>
@@ -838,6 +845,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="J15" s="2">
         <v>11</v>
       </c>
@@ -854,6 +862,7 @@
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
       <c r="J16" s="2">
         <v>12</v>
       </c>
@@ -870,6 +879,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
       <c r="J17" s="2">
         <v>13</v>
       </c>
@@ -886,6 +896,7 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
       <c r="J18" s="2">
         <v>14</v>
       </c>
@@ -920,6 +931,10 @@
         <f t="shared" si="0"/>
         <v>10000</v>
       </c>
+      <c r="I19" s="9">
+        <f>SUM(I6:I18)</f>
+        <v>25000</v>
+      </c>
       <c r="J19" s="2">
         <v>15</v>
       </c>
@@ -939,8 +954,8 @@
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="10">
-        <f>SUM(C19:H19)</f>
-        <v>10000</v>
+        <f>SUM(C19:I19)</f>
+        <v>35000</v>
       </c>
       <c r="J21" s="2">
         <v>17</v>
@@ -963,13 +978,13 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="17"/>
+      <c r="C24" s="15"/>
       <c r="D24" s="10">
         <f>D21-K45</f>
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="J24" s="2">
         <v>20</v>
@@ -1121,15 +1136,14 @@
       <c r="J45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="15">
+      <c r="K45" s="13">
         <f>SUM(K5:K44)</f>
         <v>10000</v>
       </c>
-      <c r="L45" s="16"/>
+      <c r="L45" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C4:H4"/>
+  <mergeCells count="5">
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="M3:N3"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA799A3-9232-4BC0-BBE2-7D8C8EDECEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A510A4-A26C-4071-BF97-92639A121679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>data kas</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>bg ade</t>
+  </si>
+  <si>
+    <t>p</t>
   </si>
 </sst>
 </file>
@@ -259,16 +262,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -601,6 +604,7 @@
     <col min="5" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.35">
@@ -613,13 +617,13 @@
         <v>19</v>
       </c>
       <c r="E3" s="17"/>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="12"/>
+      <c r="N3" s="14"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="16" t="s">
@@ -631,18 +635,18 @@
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="11"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -664,13 +668,13 @@
       <c r="I5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>1</v>
       </c>
-      <c r="K5" s="8">
+      <c r="L5" s="8">
         <v>5000</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -689,13 +693,13 @@
       <c r="I6" s="9">
         <v>25000</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>2</v>
       </c>
-      <c r="K6" s="8">
+      <c r="L6" s="8">
         <v>5000</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -710,11 +714,11 @@
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>3</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="2"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
@@ -727,11 +731,11 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>4</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="2"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
@@ -744,11 +748,11 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <v>5</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="2"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -761,11 +765,11 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <v>6</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
@@ -778,11 +782,11 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
-      <c r="J11" s="2">
+      <c r="K11" s="2">
         <v>7</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="2"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
@@ -795,11 +799,11 @@
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="9"/>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <v>8</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="2"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="2"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -812,11 +816,11 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="2">
+      <c r="K13" s="2">
         <v>9</v>
       </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="2"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
@@ -829,11 +833,14 @@
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="2">
+      <c r="K14" s="2">
         <v>10</v>
       </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="2"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="2"/>
+      <c r="N14" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
@@ -846,11 +853,11 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="2">
+      <c r="K15" s="2">
         <v>11</v>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="2"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="2"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
@@ -863,13 +870,13 @@
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
-      <c r="J16" s="2">
+      <c r="K16" s="2">
         <v>12</v>
       </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="L16" s="8"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>4</v>
       </c>
@@ -880,13 +887,13 @@
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="2">
+      <c r="K17" s="2">
         <v>13</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="L17" s="8"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -897,13 +904,13 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="2">
+      <c r="K18" s="2">
         <v>14</v>
       </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="L18" s="8"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
@@ -935,20 +942,20 @@
         <f>SUM(I6:I18)</f>
         <v>25000</v>
       </c>
-      <c r="J19" s="2">
+      <c r="K19" s="2">
         <v>15</v>
       </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J20" s="2">
+      <c r="L19" s="8"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K20" s="2">
         <v>16</v>
       </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="L20" s="8"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -957,197 +964,196 @@
         <f>SUM(C19:I19)</f>
         <v>35000</v>
       </c>
-      <c r="J21" s="2">
+      <c r="K21" s="2">
         <v>17</v>
       </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J22" s="2">
+      <c r="L21" s="8"/>
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K22" s="2">
         <v>18</v>
       </c>
-      <c r="K22" s="8"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J23" s="2">
+      <c r="L22" s="8"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K23" s="2">
         <v>19</v>
       </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="L23" s="8"/>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="10">
-        <f>D21-K45</f>
+        <f>D21-L45</f>
         <v>25000</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <v>20</v>
       </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J25" s="2">
+      <c r="L24" s="8"/>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K25" s="2">
         <v>21</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J26" s="2">
+      <c r="L25" s="8"/>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K26" s="2">
         <v>22</v>
       </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J27" s="2">
+      <c r="L26" s="8"/>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K27" s="2">
         <v>23</v>
       </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J28" s="2">
+      <c r="L27" s="8"/>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K28" s="2">
         <v>24</v>
       </c>
-      <c r="K28" s="8"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J29" s="2">
+      <c r="L28" s="8"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K29" s="2">
         <v>25</v>
       </c>
-      <c r="K29" s="8"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J30" s="2">
+      <c r="L29" s="8"/>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K30" s="2">
         <v>26</v>
       </c>
-      <c r="K30" s="8"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J31" s="2">
+      <c r="L30" s="8"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K31" s="2">
         <v>27</v>
       </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="J32" s="2">
+      <c r="L31" s="8"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="K32" s="2">
         <v>28</v>
       </c>
-      <c r="K32" s="8"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J33" s="2">
+      <c r="L32" s="8"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K33" s="2">
         <v>29</v>
       </c>
-      <c r="K33" s="8"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J34" s="2">
+      <c r="L33" s="8"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K34" s="2">
         <v>30</v>
       </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J35" s="2">
+      <c r="L34" s="8"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K35" s="2">
         <v>31</v>
       </c>
-      <c r="K35" s="8"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J36" s="2">
+      <c r="L35" s="8"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K36" s="2">
         <v>32</v>
       </c>
-      <c r="K36" s="8"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J37" s="2">
+      <c r="L36" s="8"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K37" s="2">
         <v>33</v>
       </c>
-      <c r="K37" s="8"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J38" s="2">
+      <c r="L37" s="8"/>
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K38" s="2">
         <v>34</v>
       </c>
-      <c r="K38" s="8"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J39" s="2">
+      <c r="L38" s="8"/>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K39" s="2">
         <v>35</v>
       </c>
-      <c r="K39" s="8"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J40" s="2">
+      <c r="L39" s="8"/>
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K40" s="2">
         <v>36</v>
       </c>
-      <c r="K40" s="8"/>
-      <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J41" s="2">
+      <c r="L40" s="8"/>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K41" s="2">
         <v>37</v>
       </c>
-      <c r="K41" s="8"/>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J42" s="2">
+      <c r="L41" s="8"/>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K42" s="2">
         <v>38</v>
       </c>
-      <c r="K42" s="8"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J43" s="2">
+      <c r="L42" s="8"/>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K43" s="2">
         <v>39</v>
       </c>
-      <c r="K43" s="8"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J44" s="2">
+      <c r="L43" s="8"/>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K44" s="2">
         <v>40</v>
       </c>
-      <c r="K44" s="8"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="10:12" x14ac:dyDescent="0.35">
-      <c r="J45" s="2" t="s">
+      <c r="L44" s="8"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="K45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K45" s="13">
-        <f>SUM(K5:K44)</f>
+      <c r="L45" s="11">
+        <f>SUM(L5:L44)</f>
         <v>10000</v>
       </c>
-      <c r="L45" s="14"/>
+      <c r="M45" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="K45:L45"/>
     <mergeCell ref="B24:C24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A510A4-A26C-4071-BF97-92639A121679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D19BBED-103C-4A91-B86E-28EF85A91B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>data kas</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>bg ade</t>
-  </si>
-  <si>
-    <t>p</t>
   </si>
 </sst>
 </file>
@@ -601,7 +598,9 @@
     <col min="2" max="2" width="10.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.26953125" customWidth="1"/>
@@ -685,7 +684,9 @@
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="F6" s="9">
+        <v>25000</v>
+      </c>
       <c r="G6" s="9"/>
       <c r="H6" s="9">
         <v>10000</v>
@@ -838,9 +839,6 @@
       </c>
       <c r="L14" s="8"/>
       <c r="M14" s="2"/>
-      <c r="N14" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
@@ -928,7 +926,7 @@
       </c>
       <c r="F19" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="G19" s="9">
         <f t="shared" si="0"/>
@@ -962,7 +960,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:I19)</f>
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="K21" s="2">
         <v>17</v>
@@ -991,7 +989,7 @@
       <c r="C24" s="15"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D19BBED-103C-4A91-B86E-28EF85A91B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0CEB58-3DED-4F9D-8FA8-327C0FD87114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E0CEB58-3DED-4F9D-8FA8-327C0FD87114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D9AFA9-D369-4060-8A19-1CBDCC3DE9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>data kas</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>bg ade</t>
+  </si>
+  <si>
+    <t>tanggal</t>
+  </si>
+  <si>
+    <t>15/09/26</t>
   </si>
 </sst>
 </file>
@@ -245,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -265,8 +271,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -274,10 +284,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,6 +611,7 @@
     <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.26953125" customWidth="1"/>
+    <col min="14" max="14" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.35">
@@ -612,27 +620,27 @@
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="M3" s="14" t="s">
+      <c r="E3" s="15"/>
+      <c r="M3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="14"/>
+      <c r="N3" s="16"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="7"/>
       <c r="K4" s="7" t="s">
         <v>21</v>
@@ -643,9 +651,12 @@
       <c r="M4" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="N4" s="7" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="13"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -675,6 +686,9 @@
       </c>
       <c r="M5" s="2" t="s">
         <v>26</v>
+      </c>
+      <c r="N5" s="18">
+        <v>46304</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.35">
@@ -702,6 +716,9 @@
       </c>
       <c r="M6" s="2" t="s">
         <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
@@ -720,6 +737,7 @@
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
@@ -737,6 +755,7 @@
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
@@ -754,6 +773,7 @@
       </c>
       <c r="L9" s="8"/>
       <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -771,6 +791,7 @@
       </c>
       <c r="L10" s="8"/>
       <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
@@ -788,6 +809,7 @@
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
@@ -805,6 +827,7 @@
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -822,6 +845,7 @@
       </c>
       <c r="L13" s="8"/>
       <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
@@ -839,6 +863,7 @@
       </c>
       <c r="L14" s="8"/>
       <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
@@ -856,6 +881,7 @@
       </c>
       <c r="L15" s="8"/>
       <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
@@ -873,8 +899,9 @@
       </c>
       <c r="L16" s="8"/>
       <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>4</v>
       </c>
@@ -890,8 +917,9 @@
       </c>
       <c r="L17" s="8"/>
       <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
@@ -907,8 +935,9 @@
       </c>
       <c r="L18" s="8"/>
       <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
@@ -945,15 +974,17 @@
       </c>
       <c r="L19" s="8"/>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K20" s="2">
         <v>16</v>
       </c>
       <c r="L20" s="8"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -967,26 +998,29 @@
       </c>
       <c r="L21" s="8"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K22" s="2">
         <v>18</v>
       </c>
       <c r="L22" s="8"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K23" s="2">
         <v>19</v>
       </c>
       <c r="L23" s="8"/>
       <c r="M23" s="2"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="15" t="s">
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B24" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="15"/>
+      <c r="C24" s="17"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
         <v>50000</v>
@@ -996,148 +1030,169 @@
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K25" s="2">
         <v>21</v>
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K26" s="2">
         <v>22</v>
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="2"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K27" s="2">
         <v>23</v>
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="2"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K28" s="2">
         <v>24</v>
       </c>
       <c r="L28" s="8"/>
       <c r="M28" s="2"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K29" s="2">
         <v>25</v>
       </c>
       <c r="L29" s="8"/>
       <c r="M29" s="2"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K30" s="2">
         <v>26</v>
       </c>
       <c r="L30" s="8"/>
       <c r="M30" s="2"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K31" s="2">
         <v>27</v>
       </c>
       <c r="L31" s="8"/>
       <c r="M31" s="2"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
       <c r="K32" s="2">
         <v>28</v>
       </c>
       <c r="L32" s="8"/>
       <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K33" s="2">
         <v>29</v>
       </c>
       <c r="L33" s="8"/>
       <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K34" s="2">
         <v>30</v>
       </c>
       <c r="L34" s="8"/>
       <c r="M34" s="2"/>
-    </row>
-    <row r="35" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N34" s="2"/>
+    </row>
+    <row r="35" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K35" s="2">
         <v>31</v>
       </c>
       <c r="L35" s="8"/>
       <c r="M35" s="2"/>
-    </row>
-    <row r="36" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N35" s="2"/>
+    </row>
+    <row r="36" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K36" s="2">
         <v>32</v>
       </c>
       <c r="L36" s="8"/>
       <c r="M36" s="2"/>
-    </row>
-    <row r="37" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K37" s="2">
         <v>33</v>
       </c>
       <c r="L37" s="8"/>
       <c r="M37" s="2"/>
-    </row>
-    <row r="38" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K38" s="2">
         <v>34</v>
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K39" s="2">
         <v>35</v>
       </c>
       <c r="L39" s="8"/>
       <c r="M39" s="2"/>
-    </row>
-    <row r="40" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K40" s="2">
         <v>36</v>
       </c>
       <c r="L40" s="8"/>
       <c r="M40" s="2"/>
-    </row>
-    <row r="41" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K41" s="2">
         <v>37</v>
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K42" s="2">
         <v>38</v>
       </c>
       <c r="L42" s="8"/>
       <c r="M42" s="2"/>
-    </row>
-    <row r="43" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N42" s="2"/>
+    </row>
+    <row r="43" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K43" s="2">
         <v>39</v>
       </c>
       <c r="L43" s="8"/>
       <c r="M43" s="2"/>
-    </row>
-    <row r="44" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N43" s="2"/>
+    </row>
+    <row r="44" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K44" s="2">
         <v>40</v>
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="2"/>
-    </row>
-    <row r="45" spans="11:13" x14ac:dyDescent="0.35">
+      <c r="N44" s="2"/>
+    </row>
+    <row r="45" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K45" s="2" t="s">
         <v>24</v>
       </c>
@@ -1146,6 +1201,7 @@
         <v>10000</v>
       </c>
       <c r="M45" s="12"/>
+      <c r="N45" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D9AFA9-D369-4060-8A19-1CBDCC3DE9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47629D7F-BE90-4251-AA86-5766D66F7A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -272,6 +272,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -284,7 +285,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,17 +620,17 @@
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="M3" s="16" t="s">
+      <c r="E3" s="16"/>
+      <c r="M3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="16"/>
+      <c r="N3" s="17"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -656,7 +656,7 @@
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B5" s="14"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
@@ -687,7 +687,7 @@
       <c r="M5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N5" s="14">
         <v>46304</v>
       </c>
     </row>
@@ -1017,10 +1017,10 @@
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="17"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
         <v>50000</v>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47629D7F-BE90-4251-AA86-5766D66F7A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE08D4A-BF6E-4871-A1F1-750B17F117BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -696,7 +696,9 @@
         <v>3</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
+      <c r="D6" s="9">
+        <v>25000</v>
+      </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9">
         <v>25000</v>
@@ -947,7 +949,7 @@
       </c>
       <c r="D19" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
@@ -991,7 +993,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:I19)</f>
-        <v>60000</v>
+        <v>85000</v>
       </c>
       <c r="K21" s="2">
         <v>17</v>
@@ -1023,7 +1025,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE08D4A-BF6E-4871-A1F1-750B17F117BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B29157-C19B-46F6-9D2F-48FED88357C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -126,7 +126,7 @@
     <t>tanggal</t>
   </si>
   <si>
-    <t>15/09/26</t>
+    <t>15/9/2026</t>
   </si>
 </sst>
 </file>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B29157-C19B-46F6-9D2F-48FED88357C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663AC305-56B5-4C6E-8EDC-61962A228442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>data kas</t>
   </si>
@@ -117,9 +117,6 @@
     <t>uang saat ini =</t>
   </si>
   <si>
-    <t>beli galon</t>
-  </si>
-  <si>
     <t>bg ade</t>
   </si>
   <si>
@@ -127,6 +124,15 @@
   </si>
   <si>
     <t>15/9/2026</t>
+  </si>
+  <si>
+    <t>beli galon(fajri)</t>
+  </si>
+  <si>
+    <t>beli galon(rasyid)</t>
+  </si>
+  <si>
+    <t>19/9/2026</t>
   </si>
 </sst>
 </file>
@@ -652,7 +658,7 @@
         <v>23</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
@@ -676,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -685,7 +691,7 @@
         <v>5000</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N5" s="14">
         <v>46304</v>
@@ -717,10 +723,10 @@
         <v>5000</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
@@ -737,9 +743,15 @@
       <c r="K7" s="2">
         <v>3</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="L7" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
@@ -1025,7 +1037,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>75000</v>
+        <v>70000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1200,7 +1212,7 @@
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663AC305-56B5-4C6E-8EDC-61962A228442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5C27F2-D452-4337-93DC-F189810397F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>data kas</t>
   </si>
@@ -133,6 +133,15 @@
   </si>
   <si>
     <t>19/9/2026</t>
+  </si>
+  <si>
+    <t>beli galon(lutfi)</t>
+  </si>
+  <si>
+    <t>29/9/2026</t>
+  </si>
+  <si>
+    <t>24/9/2026</t>
   </si>
 </sst>
 </file>
@@ -767,9 +776,15 @@
       <c r="K8" s="2">
         <v>4</v>
       </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="L8" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
@@ -785,9 +800,15 @@
       <c r="K9" s="2">
         <v>5</v>
       </c>
-      <c r="L9" s="8"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="L9" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
@@ -1037,7 +1058,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>70000</v>
+        <v>60000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1212,7 +1233,7 @@
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5C27F2-D452-4337-93DC-F189810397F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE08BA91-9AA3-4F63-B9E9-18CE1DC267FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>data kas</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>24/9/2026</t>
+  </si>
+  <si>
+    <t>beli plastik sampah</t>
+  </si>
+  <si>
+    <t>beli kran air 2buah</t>
   </si>
 </sst>
 </file>
@@ -620,8 +626,7 @@
     <col min="2" max="2" width="10.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
@@ -714,7 +719,9 @@
       <c r="D6" s="9">
         <v>25000</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9">
+        <v>25000</v>
+      </c>
       <c r="F6" s="9">
         <v>25000</v>
       </c>
@@ -744,8 +751,12 @@
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="E7" s="9">
+        <v>25000</v>
+      </c>
+      <c r="F7" s="9">
+        <v>25000</v>
+      </c>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
@@ -824,9 +835,15 @@
       <c r="K10" s="2">
         <v>6</v>
       </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="L10" s="8">
+        <v>30000</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10" s="14">
+        <v>46122</v>
+      </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
@@ -842,9 +859,15 @@
       <c r="K11" s="2">
         <v>7</v>
       </c>
-      <c r="L11" s="8"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="L11" s="8">
+        <v>26000</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" s="14">
+        <v>46123</v>
+      </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
@@ -986,11 +1009,11 @@
       </c>
       <c r="E19" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="F19" s="9">
         <f t="shared" si="0"/>
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="G19" s="9">
         <f t="shared" si="0"/>
@@ -1026,7 +1049,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:I19)</f>
-        <v>85000</v>
+        <v>160000</v>
       </c>
       <c r="K21" s="2">
         <v>17</v>
@@ -1058,7 +1081,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>60000</v>
+        <v>79000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1233,7 +1256,7 @@
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>25000</v>
+        <v>81000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE08BA91-9AA3-4F63-B9E9-18CE1DC267FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF17A1C0-78C3-4B23-9994-35C854937494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>data kas</t>
   </si>
@@ -123,25 +123,13 @@
     <t>tanggal</t>
   </si>
   <si>
-    <t>15/9/2026</t>
-  </si>
-  <si>
     <t>beli galon(fajri)</t>
   </si>
   <si>
     <t>beli galon(rasyid)</t>
   </si>
   <si>
-    <t>19/9/2026</t>
-  </si>
-  <si>
     <t>beli galon(lutfi)</t>
-  </si>
-  <si>
-    <t>29/9/2026</t>
-  </si>
-  <si>
-    <t>24/9/2026</t>
   </si>
   <si>
     <t>beli plastik sampah</t>
@@ -631,7 +619,7 @@
     <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.26953125" customWidth="1"/>
-    <col min="14" max="14" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.35">
@@ -705,7 +693,7 @@
         <v>5000</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5" s="14">
         <v>46304</v>
@@ -739,10 +727,10 @@
         <v>5000</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="N6" s="14">
+        <v>46280</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.35">
@@ -767,10 +755,10 @@
         <v>5000</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="N7" s="14">
+        <v>46284</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.35">
@@ -791,10 +779,10 @@
         <v>5000</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="N8" s="14">
+        <v>46289</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
@@ -815,10 +803,10 @@
         <v>5000</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="N9" s="14">
+        <v>46294</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
@@ -839,10 +827,10 @@
         <v>30000</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N10" s="14">
-        <v>46122</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
@@ -863,10 +851,10 @@
         <v>26000</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="N11" s="14">
-        <v>46123</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
@@ -883,9 +871,15 @@
       <c r="K12" s="2">
         <v>8</v>
       </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="L12" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="14">
+        <v>46299</v>
+      </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
@@ -1081,7 +1075,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>79000</v>
+        <v>74000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1256,7 +1250,7 @@
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>81000</v>
+        <v>86000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\KUMPULAN TUGAS\kas musholla\kas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF17A1C0-78C3-4B23-9994-35C854937494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16959772-7911-409A-8516-482B892CD216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -614,8 +614,8 @@
     <col min="2" max="2" width="10.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="6" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.7265625" customWidth="1"/>
     <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.26953125" customWidth="1"/>
@@ -713,7 +713,9 @@
       <c r="F6" s="9">
         <v>25000</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="9">
+        <v>25000</v>
+      </c>
       <c r="H6" s="9">
         <v>10000</v>
       </c>
@@ -745,7 +747,9 @@
       <c r="F7" s="9">
         <v>25000</v>
       </c>
-      <c r="G7" s="9"/>
+      <c r="G7" s="9">
+        <v>25000</v>
+      </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="K7" s="2">
@@ -1011,7 +1015,7 @@
       </c>
       <c r="G19" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="H19" s="9">
         <f t="shared" si="0"/>
@@ -1043,7 +1047,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:I19)</f>
-        <v>160000</v>
+        <v>210000</v>
       </c>
       <c r="K21" s="2">
         <v>17</v>
@@ -1075,7 +1079,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>74000</v>
+        <v>124000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16959772-7911-409A-8516-482B892CD216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FBDDEF-8303-4F12-821E-1E94C4E4EA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>data kas</t>
   </si>
@@ -899,9 +899,15 @@
       <c r="K13" s="2">
         <v>9</v>
       </c>
-      <c r="L13" s="8"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="L13" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13" s="14">
+        <v>46304</v>
+      </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
@@ -1079,7 +1085,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>124000</v>
+        <v>119000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1254,7 +1260,7 @@
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>86000</v>
+        <v>91000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FBDDEF-8303-4F12-821E-1E94C4E4EA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F28054-4FF5-4787-A406-360543DF6633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>data kas</t>
   </si>
@@ -51,9 +51,6 @@
     <t>september</t>
   </si>
   <si>
-    <t>oktober</t>
-  </si>
-  <si>
     <t>october</t>
   </si>
   <si>
@@ -72,9 +69,6 @@
     <t>march</t>
   </si>
   <si>
-    <t>ridwan</t>
-  </si>
-  <si>
     <t>roro</t>
   </si>
   <si>
@@ -136,6 +130,24 @@
   </si>
   <si>
     <t>beli kran air 2buah</t>
+  </si>
+  <si>
+    <t>afdal</t>
+  </si>
+  <si>
+    <t>april</t>
+  </si>
+  <si>
+    <t>may</t>
+  </si>
+  <si>
+    <t>june</t>
+  </si>
+  <si>
+    <t>july</t>
+  </si>
+  <si>
+    <t>august</t>
   </si>
 </sst>
 </file>
@@ -629,11 +641,11 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D3" s="16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E3" s="16"/>
       <c r="M3" s="17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N3" s="17"/>
     </row>
@@ -651,40 +663,40 @@
       <c r="H4" s="13"/>
       <c r="I4" s="7"/>
       <c r="K4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="N4" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B5" s="15"/>
       <c r="C5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2">
         <v>1</v>
@@ -693,7 +705,7 @@
         <v>5000</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N5" s="14">
         <v>46304</v>
@@ -729,7 +741,7 @@
         <v>5000</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N6" s="14">
         <v>46280</v>
@@ -751,7 +763,9 @@
         <v>25000</v>
       </c>
       <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
+      <c r="I7" s="9">
+        <v>25000</v>
+      </c>
       <c r="K7" s="2">
         <v>3</v>
       </c>
@@ -759,7 +773,7 @@
         <v>5000</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N7" s="14">
         <v>46284</v>
@@ -775,7 +789,9 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
+      <c r="I8" s="9">
+        <v>25000</v>
+      </c>
       <c r="K8" s="2">
         <v>4</v>
       </c>
@@ -783,7 +799,7 @@
         <v>5000</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N8" s="14">
         <v>46289</v>
@@ -791,7 +807,7 @@
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -807,7 +823,7 @@
         <v>5000</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N9" s="14">
         <v>46294</v>
@@ -815,7 +831,7 @@
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -831,7 +847,7 @@
         <v>30000</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N10" s="14">
         <v>46299</v>
@@ -839,7 +855,7 @@
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -855,7 +871,7 @@
         <v>26000</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N11" s="14">
         <v>46299</v>
@@ -863,7 +879,7 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -879,7 +895,7 @@
         <v>5000</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N12" s="14">
         <v>46299</v>
@@ -887,7 +903,7 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -903,7 +919,7 @@
         <v>5000</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N13" s="14">
         <v>46304</v>
@@ -911,7 +927,7 @@
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -923,13 +939,19 @@
       <c r="K14" s="2">
         <v>10</v>
       </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="L14" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="14">
+        <v>46310</v>
+      </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -947,7 +969,7 @@
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -965,7 +987,7 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -983,7 +1005,7 @@
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -1001,7 +1023,7 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C19" s="9">
         <f t="shared" ref="C19:H19" si="0">SUM(C6:C18)</f>
@@ -1029,7 +1051,7 @@
       </c>
       <c r="I19" s="9">
         <f>SUM(I6:I18)</f>
-        <v>25000</v>
+        <v>75000</v>
       </c>
       <c r="K19" s="2">
         <v>15</v>
@@ -1048,12 +1070,12 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B21" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:I19)</f>
-        <v>210000</v>
+        <v>260000</v>
       </c>
       <c r="K21" s="2">
         <v>17</v>
@@ -1080,12 +1102,12 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>119000</v>
+        <v>164000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1256,11 +1278,11 @@
     </row>
     <row r="45" spans="11:14" x14ac:dyDescent="0.35">
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>91000</v>
+        <v>96000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F28054-4FF5-4787-A406-360543DF6633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8208ED57-2C6D-4D9A-9249-C5CD30441E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -729,7 +729,7 @@
         <v>25000</v>
       </c>
       <c r="H6" s="9">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="I6" s="9">
         <v>25000</v>
@@ -762,7 +762,9 @@
       <c r="G7" s="9">
         <v>25000</v>
       </c>
-      <c r="H7" s="9"/>
+      <c r="H7" s="9">
+        <v>25000</v>
+      </c>
       <c r="I7" s="9">
         <v>25000</v>
       </c>
@@ -1047,7 +1049,7 @@
       </c>
       <c r="H19" s="9">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="I19" s="9">
         <f>SUM(I6:I18)</f>
@@ -1075,7 +1077,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="10">
         <f>SUM(C19:I19)</f>
-        <v>260000</v>
+        <v>300000</v>
       </c>
       <c r="K21" s="2">
         <v>17</v>
@@ -1107,7 +1109,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>164000</v>
+        <v>204000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8208ED57-2C6D-4D9A-9249-C5CD30441E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F68F98-3999-441E-87BC-6FDA1FF30F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>data kas</t>
   </si>
@@ -631,6 +631,7 @@
     <col min="8" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.26953125" customWidth="1"/>
+    <col min="13" max="13" width="15.90625" customWidth="1"/>
     <col min="14" max="14" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -965,9 +966,15 @@
       <c r="K15" s="2">
         <v>11</v>
       </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="L15" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="14">
+        <v>46315</v>
+      </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
@@ -1109,7 +1116,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>204000</v>
+        <v>199000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1284,7 +1291,7 @@
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>96000</v>
+        <v>101000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>

--- a/kas.xlsx
+++ b/kas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KUMPULAN TUGAS\kas musholla\kas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F68F98-3999-441E-87BC-6FDA1FF30F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD2FA5B-F638-4543-AFA0-9A938538FDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0497A79C-2985-4487-AEE7-CEAA57854CDA}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>data kas</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>august</t>
+  </si>
+  <si>
+    <t>bayar pemasangan wifi</t>
   </si>
 </sst>
 </file>
@@ -990,9 +993,15 @@
       <c r="K16" s="2">
         <v>12</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="L16" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="14">
+        <v>46321</v>
+      </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
@@ -1008,9 +1017,15 @@
       <c r="K17" s="2">
         <v>13</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="L17" s="8">
+        <v>111000</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="14">
+        <v>46297</v>
+      </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
@@ -1116,7 +1131,7 @@
       <c r="C24" s="18"/>
       <c r="D24" s="10">
         <f>D21-L45</f>
-        <v>199000</v>
+        <v>83000</v>
       </c>
       <c r="K24" s="2">
         <v>20</v>
@@ -1291,7 +1306,7 @@
       </c>
       <c r="L45" s="11">
         <f>SUM(L5:L44)</f>
-        <v>101000</v>
+        <v>217000</v>
       </c>
       <c r="M45" s="12"/>
       <c r="N45" s="2"/>
